--- a/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة عشيرة قرنبالية المدينة.xlsx
+++ b/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة عشيرة قرنبالية المدينة.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>المعرف</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>ملازم قائد الوحدة</t>
+  </si>
+  <si>
+    <t>code_unite</t>
+  </si>
+  <si>
+    <t>CHFA</t>
   </si>
 </sst>
 </file>
@@ -449,6 +455,9 @@
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -481,8 +490,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>19</v>
       </c>
       <c r="B2">
         <v>900001443</v>
@@ -516,8 +525,8 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
         <v>900008602</v>
@@ -553,7 +562,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A3:K3 A2:D2 F2:K2" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:K1 B3:K3 B2:D2 F2:K2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>